--- a/validation_results.xlsx
+++ b/validation_results.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nitis\Documents\Novac\Doc_Class\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF7A2B72-066B-4D52-957E-234674CC2E66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BC8095E-DBF7-4E10-853B-429FE6A6DB46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$328</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
@@ -1394,7 +1397,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.77734375" customWidth="1"/>
-    <col min="2" max="2" width="44.5546875" customWidth="1"/>
+    <col min="2" max="2" width="67.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
@@ -5990,6 +5993,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:D328" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>